--- a/日報/日報_テスト太郎.xlsx
+++ b/日報/日報_テスト太郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\日報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6FD047-CCFC-40FC-81A3-53B80023AF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92054EE-7A54-4E79-9C0F-17C87B8FDCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="5">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -56,29 +56,6 @@
   </si>
   <si>
     <t>テスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特許</t>
-    <rPh sb="0" eb="2">
-      <t>トッキョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トヨタ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あああああああ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>いいいいいい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NG</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -478,7 +455,7 @@
         <v>0.75</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -520,7 +497,7 @@
         <v>0.75</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -604,7 +581,7 @@
         <v>0.75</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -632,7 +609,7 @@
         <v>0.75</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -685,7 +662,7 @@
         <v>0.375</v>
       </c>
       <c r="C30" s="1">
-        <v>0.75</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
@@ -702,7 +679,7 @@
         <v>0.75</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -758,7 +735,7 @@
         <v>0.75</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -828,7 +805,7 @@
         <v>0.75</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -842,7 +819,7 @@
         <v>0.75</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:4">

--- a/日報/日報_テスト太郎.xlsx
+++ b/日報/日報_テスト太郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\日報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92054EE-7A54-4E79-9C0F-17C87B8FDCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E67EC6-DF81-47CA-9A66-6FBD63C45B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7410" yWindow="7410" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
